--- a/01_data/01_input_data/02_processed/01_paper_IAEE/inputs_IAEE_2025_run_2024.xlsx
+++ b/01_data/01_input_data/02_processed/01_paper_IAEE/inputs_IAEE_2025_run_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\01_paper_IAEE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9506FF-15A3-4B91-9540-F8303C9C8CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847FFFF4-D17D-4A71-91E9-542C10C666EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="Parameters" sheetId="4" r:id="rId4"/>
     <sheet name="Supply" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -9026,10 +9039,10 @@
         <v>60</v>
       </c>
       <c r="D134">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E134">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F134">
         <v>2217.8919619330381</v>
@@ -9055,10 +9068,10 @@
         <v>62</v>
       </c>
       <c r="D135">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E135">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F135">
         <v>2217.8919619330381</v>
@@ -9084,10 +9097,10 @@
         <v>64</v>
       </c>
       <c r="D136">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E136">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F136">
         <v>2217.8919619330381</v>
@@ -9113,10 +9126,10 @@
         <v>66</v>
       </c>
       <c r="D137">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E137">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F137">
         <v>2217.8919619330381</v>
@@ -9142,10 +9155,10 @@
         <v>68</v>
       </c>
       <c r="D138">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E138">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F138">
         <v>2217.8919619330381</v>
@@ -9171,10 +9184,10 @@
         <v>70</v>
       </c>
       <c r="D139">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E139">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F139">
         <v>2217.8919619330381</v>
@@ -9200,10 +9213,10 @@
         <v>72</v>
       </c>
       <c r="D140">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E140">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F140">
         <v>2217.8919619330381</v>
@@ -9229,10 +9242,10 @@
         <v>74</v>
       </c>
       <c r="D141">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E141">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F141">
         <v>8530.3536997424526</v>
@@ -9258,10 +9271,10 @@
         <v>76</v>
       </c>
       <c r="D142">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E142">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F142">
         <v>8530.3536997424526</v>
@@ -9287,10 +9300,10 @@
         <v>78</v>
       </c>
       <c r="D143">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E143">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F143">
         <v>8530.3536997424526</v>
@@ -9316,10 +9329,10 @@
         <v>80</v>
       </c>
       <c r="D144">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E144">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F144">
         <v>8530.3536997424526</v>
@@ -9345,10 +9358,10 @@
         <v>81</v>
       </c>
       <c r="D145">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E145">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F145">
         <v>8530.3536997424526</v>
@@ -9374,10 +9387,10 @@
         <v>83</v>
       </c>
       <c r="D146">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E146">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F146">
         <v>8530.3536997424526</v>
@@ -9403,10 +9416,10 @@
         <v>84</v>
       </c>
       <c r="D147">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E147">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F147">
         <v>8530.3536997424526</v>
@@ -9432,10 +9445,10 @@
         <v>86</v>
       </c>
       <c r="D148">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E148">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F148">
         <v>8530.3536997424526</v>
@@ -9461,10 +9474,10 @@
         <v>87</v>
       </c>
       <c r="D149">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E149">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F149">
         <v>8530.3536997424526</v>
@@ -9809,10 +9822,10 @@
         <v>45</v>
       </c>
       <c r="D161">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E161">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F161">
         <v>540.46946163351765</v>
@@ -9838,10 +9851,10 @@
         <v>53</v>
       </c>
       <c r="D162">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E162">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F162">
         <v>1172.5937663823611</v>
@@ -9867,10 +9880,10 @@
         <v>71</v>
       </c>
       <c r="D163">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E163">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F163">
         <v>1048.1635700088191</v>
@@ -9896,10 +9909,10 @@
         <v>61</v>
       </c>
       <c r="D164">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E164">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F164">
         <v>1339.44499037841</v>
@@ -9925,10 +9938,10 @@
         <v>47</v>
       </c>
       <c r="D165">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E165">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F165">
         <v>563.26970737836405</v>
@@ -9954,10 +9967,10 @@
         <v>49</v>
       </c>
       <c r="D166">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E166">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F166">
         <v>659.52301753984625</v>
@@ -9983,10 +9996,10 @@
         <v>46</v>
       </c>
       <c r="D167">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E167">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F167">
         <v>1170.9097511316411</v>
@@ -10012,10 +10025,10 @@
         <v>43</v>
       </c>
       <c r="D168">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E168">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F168">
         <v>435.1478719144261</v>
@@ -10041,10 +10054,10 @@
         <v>57</v>
       </c>
       <c r="D169">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E169">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F169">
         <v>515.59646627550342</v>
@@ -10070,10 +10083,10 @@
         <v>61</v>
       </c>
       <c r="D170">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E170">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F170">
         <v>283.18941589905791</v>
@@ -10099,10 +10112,10 @@
         <v>63</v>
       </c>
       <c r="D171">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E171">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F171">
         <v>922.63267156134054</v>
@@ -10128,10 +10141,10 @@
         <v>46</v>
       </c>
       <c r="D172">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E172">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F172">
         <v>1263.2718800070211</v>
@@ -10157,10 +10170,10 @@
         <v>65</v>
       </c>
       <c r="D173">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E173">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F173">
         <v>1152.3856014712901</v>
@@ -10186,10 +10199,10 @@
         <v>42</v>
       </c>
       <c r="D174">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E174">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F174">
         <v>813.13009287949433</v>
@@ -10215,10 +10228,10 @@
         <v>61</v>
       </c>
       <c r="D175">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E175">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F175">
         <v>304.8237399864974</v>
@@ -10244,10 +10257,10 @@
         <v>44</v>
       </c>
       <c r="D176">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E176">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F176">
         <v>661.85486085466005</v>
@@ -10273,10 +10286,10 @@
         <v>56</v>
       </c>
       <c r="D177">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E177">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F177">
         <v>925.56533140178669</v>
@@ -10302,10 +10315,10 @@
         <v>56</v>
       </c>
       <c r="D178">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E178">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F178">
         <v>624.8044615192847</v>
@@ -10331,10 +10344,10 @@
         <v>55</v>
       </c>
       <c r="D179">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E179">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F179">
         <v>682.30581336702562</v>
@@ -10360,10 +10373,10 @@
         <v>48</v>
       </c>
       <c r="D180">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E180">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F180">
         <v>564.04698848330202</v>
@@ -10389,10 +10402,10 @@
         <v>69</v>
       </c>
       <c r="D181">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E181">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F181">
         <v>566.37883179811581</v>
@@ -10418,10 +10431,10 @@
         <v>45</v>
       </c>
       <c r="D182">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E182">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F182">
         <v>729.47831698426114</v>
@@ -10447,10 +10460,10 @@
         <v>59</v>
       </c>
       <c r="D183">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E183">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F183">
         <v>843.6090925593162</v>
@@ -10476,10 +10489,10 @@
         <v>69</v>
       </c>
       <c r="D184">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E184">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F184">
         <v>1446.961628704282</v>
@@ -10505,10 +10518,10 @@
         <v>51</v>
       </c>
       <c r="D185">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E185">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F185">
         <v>560.68564654089403</v>
@@ -10534,10 +10547,10 @@
         <v>47</v>
       </c>
       <c r="D186">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E186">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F186">
         <v>645.92059820343218</v>
@@ -10563,10 +10576,10 @@
         <v>49</v>
       </c>
       <c r="D187">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E187">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F187">
         <v>705.12350902953904</v>
@@ -10592,10 +10605,10 @@
         <v>71</v>
       </c>
       <c r="D188">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E188">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F188">
         <v>1022.513293545866</v>
@@ -10621,10 +10634,10 @@
         <v>57</v>
       </c>
       <c r="D189">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E189">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F189">
         <v>642.29328638038839</v>
@@ -10650,10 +10663,10 @@
         <v>49</v>
       </c>
       <c r="D190">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E190">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F190">
         <v>1292.9367197555321</v>
@@ -10679,10 +10692,10 @@
         <v>52</v>
       </c>
       <c r="D191">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E191">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F191">
         <v>466.66213718098783</v>
@@ -10708,10 +10721,10 @@
         <v>57</v>
       </c>
       <c r="D192">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E192">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F192">
         <v>1152.6446802547839</v>
@@ -10737,10 +10750,10 @@
         <v>50</v>
       </c>
       <c r="D193">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E193">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F193">
         <v>945.25473128683257</v>
@@ -10766,10 +10779,10 @@
         <v>67</v>
       </c>
       <c r="D194">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E194">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F194">
         <v>711.70831606185914</v>
@@ -10795,10 +10808,10 @@
         <v>54</v>
       </c>
       <c r="D195">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E195">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F195">
         <v>953.02688240405632</v>
@@ -10824,10 +10837,10 @@
         <v>48</v>
       </c>
       <c r="D196">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E196">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F196">
         <v>999999</v>
@@ -10853,10 +10866,10 @@
         <v>54</v>
       </c>
       <c r="D197">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E197">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F197">
         <v>652.26839389375868</v>
@@ -10882,10 +10895,10 @@
         <v>42</v>
       </c>
       <c r="D198">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E198">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F198">
         <v>999999</v>
@@ -10911,10 +10924,10 @@
         <v>58</v>
       </c>
       <c r="D199">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E199">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F199">
         <v>838.64795994697079</v>
@@ -10940,10 +10953,10 @@
         <v>53</v>
       </c>
       <c r="D200">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E200">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F200">
         <v>604.46560594007508</v>
@@ -10969,10 +10982,10 @@
         <v>48</v>
       </c>
       <c r="D201">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E201">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F201">
         <v>1437.5050563038239</v>
@@ -10998,10 +11011,10 @@
         <v>58</v>
       </c>
       <c r="D202">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E202">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F202">
         <v>550.31502229606497</v>
@@ -11027,10 +11040,10 @@
         <v>46</v>
       </c>
       <c r="D203">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E203">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F203">
         <v>537.48988406458886</v>
@@ -11056,10 +11069,10 @@
         <v>56</v>
       </c>
       <c r="D204">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E204">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F204">
         <v>934.24420266997026</v>
@@ -11085,10 +11098,10 @@
         <v>69</v>
       </c>
       <c r="D205">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E205">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F205">
         <v>1535.5686247495651</v>
@@ -11114,10 +11127,10 @@
         <v>61</v>
       </c>
       <c r="D206">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E206">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F206">
         <v>1205.5629937587521</v>
@@ -11143,10 +11156,10 @@
         <v>52</v>
       </c>
       <c r="D207">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E207">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F207">
         <v>999999</v>
@@ -11172,10 +11185,10 @@
         <v>55</v>
       </c>
       <c r="D208">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E208">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F208">
         <v>673.62761896556322</v>
@@ -11201,10 +11214,10 @@
         <v>47</v>
       </c>
       <c r="D209">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E209">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F209">
         <v>516.24420052961841</v>
@@ -11230,10 +11243,10 @@
         <v>63</v>
       </c>
       <c r="D210">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E210">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F210">
         <v>665.22307897605776</v>
@@ -11259,10 +11272,10 @@
         <v>59</v>
       </c>
       <c r="D211">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E211">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F211">
         <v>834.92945355417578</v>
@@ -11288,10 +11301,10 @@
         <v>50</v>
       </c>
       <c r="D212">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E212">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F212">
         <v>999999</v>
@@ -11317,10 +11330,10 @@
         <v>54</v>
       </c>
       <c r="D213">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E213">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F213">
         <v>999999</v>
@@ -11346,10 +11359,10 @@
         <v>65</v>
       </c>
       <c r="D214">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E214">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F214">
         <v>394.40505405731869</v>
@@ -11375,10 +11388,10 @@
         <v>67</v>
       </c>
       <c r="D215">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E215">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F215">
         <v>376.46314849161132</v>
@@ -11404,10 +11417,10 @@
         <v>43</v>
       </c>
       <c r="D216">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E216">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F216">
         <v>472.19827124980151</v>
@@ -11433,10 +11446,10 @@
         <v>46</v>
       </c>
       <c r="D217">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E217">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F217">
         <v>591.25182715613005</v>
@@ -11462,10 +11475,10 @@
         <v>51</v>
       </c>
       <c r="D218">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E218">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F218">
         <v>162.96993833532241</v>
@@ -11491,10 +11504,10 @@
         <v>63</v>
       </c>
       <c r="D219">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E219">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F219">
         <v>802.41319399760505</v>
@@ -11520,10 +11533,10 @@
         <v>58</v>
       </c>
       <c r="D220">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E220">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F220">
         <v>847.32666469581557</v>
@@ -11549,10 +11562,10 @@
         <v>65</v>
       </c>
       <c r="D221">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E221">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F221">
         <v>1239.565964164552</v>
@@ -11578,10 +11591,10 @@
         <v>44</v>
       </c>
       <c r="D222">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E222">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F222">
         <v>654.4706903577495</v>
@@ -11607,10 +11620,10 @@
         <v>48</v>
       </c>
       <c r="D223">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E223">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F223">
         <v>711.7303984215115</v>
@@ -11636,10 +11649,10 @@
         <v>63</v>
       </c>
       <c r="D224">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E224">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F224">
         <v>1082.2343917752651</v>
@@ -11665,10 +11678,10 @@
         <v>71</v>
       </c>
       <c r="D225">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E225">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F225">
         <v>775.72654272806903</v>
@@ -11694,10 +11707,10 @@
         <v>65</v>
       </c>
       <c r="D226">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E226">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F226">
         <v>487.0961590944454</v>
@@ -11723,10 +11736,10 @@
         <v>63</v>
       </c>
       <c r="D227">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E227">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F227">
         <v>1108.143761939863</v>
@@ -11752,10 +11765,10 @@
         <v>55</v>
       </c>
       <c r="D228">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E228">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F228">
         <v>999999</v>
@@ -11781,10 +11794,10 @@
         <v>45</v>
       </c>
       <c r="D229">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E229">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F229">
         <v>567.54997885355817</v>
@@ -11810,10 +11823,10 @@
         <v>65</v>
       </c>
       <c r="D230">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E230">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F230">
         <v>579.98125113452977</v>
@@ -11839,10 +11852,10 @@
         <v>71</v>
       </c>
       <c r="D231">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E231">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F231">
         <v>689.5778869307801</v>
@@ -11868,10 +11881,10 @@
         <v>59</v>
       </c>
       <c r="D232">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E232">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F232">
         <v>122.9399614310183</v>
@@ -11897,10 +11910,10 @@
         <v>47</v>
       </c>
       <c r="D233">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E233">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F233">
         <v>813.25962474591165</v>
@@ -11926,10 +11939,10 @@
         <v>49</v>
       </c>
       <c r="D234">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E234">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F234">
         <v>909.50298144548663</v>
@@ -11955,10 +11968,10 @@
         <v>51</v>
       </c>
       <c r="D235">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E235">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F235">
         <v>999999</v>
@@ -11984,10 +11997,10 @@
         <v>42</v>
       </c>
       <c r="D236">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E236">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F236">
         <v>424.13638959447189</v>
@@ -12013,10 +12026,10 @@
         <v>43</v>
       </c>
       <c r="D237">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E237">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F237">
         <v>603.42644023070341</v>
@@ -12042,10 +12055,10 @@
         <v>51</v>
       </c>
       <c r="D238">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E238">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F238">
         <v>1036.448594390177</v>
@@ -12071,10 +12084,10 @@
         <v>71</v>
       </c>
       <c r="D239">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E239">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F239">
         <v>1187.0377940910651</v>
@@ -12100,10 +12113,10 @@
         <v>57</v>
       </c>
       <c r="D240">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E240">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F240">
         <v>593.5829824828146</v>
@@ -12129,10 +12142,10 @@
         <v>56</v>
       </c>
       <c r="D241">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E241">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F241">
         <v>536.58305610882792</v>
@@ -12158,10 +12171,10 @@
         <v>69</v>
       </c>
       <c r="D242">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E242">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F242">
         <v>777.50901913587666</v>
@@ -12187,10 +12200,10 @@
         <v>48</v>
       </c>
       <c r="D243">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E243">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F243">
         <v>757.33088991120428</v>
@@ -12216,10 +12229,10 @@
         <v>53</v>
       </c>
       <c r="D244">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E244">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F244">
         <v>780.48822113226493</v>
@@ -12245,10 +12258,10 @@
         <v>53</v>
       </c>
       <c r="D245">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E245">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F245">
         <v>514.81918517056545</v>
@@ -12274,10 +12287,10 @@
         <v>71</v>
       </c>
       <c r="D246">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E246">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F246">
         <v>1110.8642458071461</v>
@@ -12303,10 +12316,10 @@
         <v>42</v>
       </c>
       <c r="D247">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E247">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F247">
         <v>654.4706903577495</v>
@@ -12332,10 +12345,10 @@
         <v>44</v>
       </c>
       <c r="D248">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E248">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F248">
         <v>475.20927891091247</v>
@@ -12361,10 +12374,10 @@
         <v>67</v>
       </c>
       <c r="D249">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E249">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F249">
         <v>377.62907014901822</v>
@@ -12390,10 +12403,10 @@
         <v>46</v>
       </c>
       <c r="D250">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E250">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F250">
         <v>466.23911611194387</v>
@@ -12419,10 +12432,10 @@
         <v>48</v>
       </c>
       <c r="D251">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E251">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F251">
         <v>1345.141804878509</v>
@@ -12448,10 +12461,10 @@
         <v>42</v>
       </c>
       <c r="D252">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E252">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F252">
         <v>1205.2378061193219</v>
@@ -12477,10 +12490,10 @@
         <v>61</v>
       </c>
       <c r="D253">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E253">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F253">
         <v>1263.145525883135</v>
@@ -12506,10 +12519,10 @@
         <v>52</v>
       </c>
       <c r="D254">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E254">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F254">
         <v>67.105268726309248</v>
@@ -12535,10 +12548,10 @@
         <v>56</v>
       </c>
       <c r="D255">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E255">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F255">
         <v>999999</v>
@@ -12564,10 +12577,10 @@
         <v>50</v>
       </c>
       <c r="D256">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E256">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F256">
         <v>556.27417743392255</v>
@@ -12593,10 +12606,10 @@
         <v>69</v>
       </c>
       <c r="D257">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E257">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F257">
         <v>229.94566021080871</v>
@@ -12622,10 +12635,10 @@
         <v>42</v>
       </c>
       <c r="D258">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E258">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F258">
         <v>1297.6001937905601</v>
@@ -12651,10 +12664,10 @@
         <v>54</v>
       </c>
       <c r="D259">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E259">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F259">
         <v>564.04698848330202</v>
@@ -12680,10 +12693,10 @@
         <v>56</v>
       </c>
       <c r="D260">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E260">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F260">
         <v>1410.0421601576891</v>
@@ -12709,10 +12722,10 @@
         <v>58</v>
       </c>
       <c r="D261">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E261">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F261">
         <v>449.65711920660112</v>
@@ -12738,10 +12751,10 @@
         <v>65</v>
       </c>
       <c r="D262">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E262">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F262">
         <v>910.71436128562539</v>
@@ -12767,10 +12780,10 @@
         <v>69</v>
       </c>
       <c r="D263">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E263">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F263">
         <v>338.376374349652</v>
@@ -12796,10 +12809,10 @@
         <v>52</v>
       </c>
       <c r="D264">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E264">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F264">
         <v>872.8447549607946</v>
@@ -12825,10 +12838,10 @@
         <v>45</v>
       </c>
       <c r="D265">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E265">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F265">
         <v>568.19755943350117</v>
@@ -12854,10 +12867,10 @@
         <v>45</v>
       </c>
       <c r="D266">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E266">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F266">
         <v>657.45026792667841</v>
@@ -12883,10 +12896,10 @@
         <v>47</v>
       </c>
       <c r="D267">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E267">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F267">
         <v>804.58100036600638</v>
@@ -12912,10 +12925,10 @@
         <v>53</v>
       </c>
       <c r="D268">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E268">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F268">
         <v>789.1667822439731</v>
@@ -12941,10 +12954,10 @@
         <v>49</v>
       </c>
       <c r="D269">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E269">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F269">
         <v>900.82415272953961</v>
@@ -12970,10 +12983,10 @@
         <v>49</v>
       </c>
       <c r="D270">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E270">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F270">
         <v>600.06101301209344</v>
@@ -12999,10 +13012,10 @@
         <v>67</v>
       </c>
       <c r="D271">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E271">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F271">
         <v>800.30646211998305</v>
@@ -13028,10 +13041,10 @@
         <v>54</v>
       </c>
       <c r="D272">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E272">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F272">
         <v>1345.141804878509</v>
@@ -13057,10 +13070,10 @@
         <v>50</v>
       </c>
       <c r="D273">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E273">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F273">
         <v>1337.3693242725089</v>
@@ -13086,10 +13099,10 @@
         <v>43</v>
       </c>
       <c r="D274">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E274">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F274">
         <v>594.74865147578487</v>
@@ -13115,10 +13128,10 @@
         <v>52</v>
       </c>
       <c r="D275">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E275">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F275">
         <v>951.08384361341189</v>
@@ -13144,10 +13157,10 @@
         <v>46</v>
       </c>
       <c r="D276">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E276">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F276">
         <v>787.48288046864025</v>
@@ -13173,10 +13186,10 @@
         <v>57</v>
       </c>
       <c r="D277">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E277">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F277">
         <v>800.30646211998305</v>
@@ -13202,10 +13215,10 @@
         <v>71</v>
       </c>
       <c r="D278">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E278">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F278">
         <v>439.42291799158482</v>
@@ -13231,10 +13244,10 @@
         <v>57</v>
       </c>
       <c r="D279">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E279">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F279">
         <v>511.96915445245958</v>
@@ -13260,10 +13273,10 @@
         <v>61</v>
       </c>
       <c r="D280">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E280">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F280">
         <v>757.2013430603813</v>
@@ -13289,10 +13302,10 @@
         <v>50</v>
       </c>
       <c r="D281">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E281">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F281">
         <v>1429.732534487347</v>
@@ -13318,10 +13331,10 @@
         <v>55</v>
       </c>
       <c r="D282">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E282">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F282">
         <v>269.71654341346692</v>
@@ -13347,10 +13360,10 @@
         <v>54</v>
       </c>
       <c r="D283">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E283">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F283">
         <v>1437.5050563038239</v>
@@ -13376,10 +13389,10 @@
         <v>58</v>
       </c>
       <c r="D284">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E284">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F284">
         <v>999999</v>
@@ -13405,10 +13418,10 @@
         <v>59</v>
       </c>
       <c r="D285">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E285">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F285">
         <v>1046.0343850694751</v>
@@ -13434,10 +13447,10 @@
         <v>44</v>
       </c>
       <c r="D286">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E286">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F286">
         <v>466.53263586554471</v>
@@ -13463,10 +13476,10 @@
         <v>58</v>
       </c>
       <c r="D287">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E287">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F287">
         <v>1323.1197865788711</v>
@@ -13492,10 +13505,10 @@
         <v>42</v>
       </c>
       <c r="D288">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E288">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F288">
         <v>571.81979953268137</v>
@@ -13521,10 +13534,10 @@
         <v>51</v>
       </c>
       <c r="D289">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E289">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F289">
         <v>826.50890825068143</v>
@@ -13550,10 +13563,10 @@
         <v>56</v>
       </c>
       <c r="D290">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E290">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F290">
         <v>684.26646604703751</v>
@@ -13579,10 +13592,10 @@
         <v>55</v>
       </c>
       <c r="D291">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E291">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F291">
         <v>1065.7241554400659</v>
@@ -13608,10 +13621,10 @@
         <v>45</v>
       </c>
       <c r="D292">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E292">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F292">
         <v>999999</v>
@@ -13637,10 +13650,10 @@
         <v>47</v>
       </c>
       <c r="D293">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E293">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F293">
         <v>999999</v>
@@ -13666,10 +13679,10 @@
         <v>59</v>
       </c>
       <c r="D294">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E294">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F294">
         <v>344.20598263668649</v>
@@ -13695,10 +13708,10 @@
         <v>69</v>
       </c>
       <c r="D295">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E295">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F295">
         <v>1141.048662048903</v>
@@ -13724,10 +13737,10 @@
         <v>51</v>
       </c>
       <c r="D296">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E296">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F296">
         <v>944.08890955657546</v>
@@ -13753,10 +13766,10 @@
         <v>43</v>
       </c>
       <c r="D297">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E297">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F297">
         <v>999999</v>
@@ -13782,10 +13795,10 @@
         <v>55</v>
       </c>
       <c r="D298">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E298">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F298">
         <v>1158.085336250198</v>
@@ -13811,10 +13824,10 @@
         <v>59</v>
       </c>
       <c r="D299">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E299">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F299">
         <v>392.91559854613121</v>
@@ -13840,10 +13853,10 @@
         <v>48</v>
       </c>
       <c r="D300">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E300">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F300">
         <v>961.70579709298238</v>
@@ -13869,10 +13882,10 @@
         <v>52</v>
       </c>
       <c r="D301">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E301">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F301">
         <v>624.93400837010768</v>
@@ -13898,10 +13911,10 @@
         <v>44</v>
       </c>
       <c r="D302">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E302">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F302">
         <v>999999</v>
@@ -13927,10 +13940,10 @@
         <v>50</v>
       </c>
       <c r="D303">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E303">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F303">
         <v>703.95758737213202</v>
@@ -13956,10 +13969,10 @@
         <v>54</v>
       </c>
       <c r="D304">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E304">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F304">
         <v>711.7303984215115</v>
@@ -13985,10 +13998,10 @@
         <v>46</v>
       </c>
       <c r="D305">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E305">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F305">
         <v>778.80432399854487</v>
@@ -14014,10 +14027,10 @@
         <v>56</v>
       </c>
       <c r="D306">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E306">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F306">
         <v>729.8669575367303</v>
@@ -14043,10 +14056,10 @@
         <v>61</v>
       </c>
       <c r="D307">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E307">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F307">
         <v>647.86380096577705</v>
@@ -14072,10 +14085,10 @@
         <v>58</v>
       </c>
       <c r="D308">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E308">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F308">
         <v>597.3405291448106</v>
@@ -14101,10 +14114,10 @@
         <v>69</v>
       </c>
       <c r="D309">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E309">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F309">
         <v>1574.1749217874089</v>
@@ -14130,10 +14143,10 @@
         <v>63</v>
       </c>
       <c r="D310">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E310">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F310">
         <v>540.72855533516361</v>
@@ -14159,10 +14172,10 @@
         <v>53</v>
       </c>
       <c r="D311">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E311">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F311">
         <v>376.5926953424343</v>
@@ -14188,10 +14201,10 @@
         <v>56</v>
       </c>
       <c r="D312">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E312">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F312">
         <v>1317.6790575192831</v>
@@ -14217,10 +14230,10 @@
         <v>65</v>
       </c>
       <c r="D313">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E313">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F313">
         <v>1063.7810837712</v>
@@ -14246,10 +14259,10 @@
         <v>52</v>
       </c>
       <c r="D314">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E314">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F314">
         <v>810.3155518978075</v>
@@ -14275,10 +14288,10 @@
         <v>67</v>
       </c>
       <c r="D315">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E315">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F315">
         <v>887.48210367763295</v>
@@ -14304,10 +14317,10 @@
         <v>50</v>
       </c>
       <c r="D316">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E316">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F316">
         <v>749.55807886182481</v>
@@ -14333,10 +14346,10 @@
         <v>55</v>
       </c>
       <c r="D317">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E317">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F317">
         <v>439.03427743911578</v>
@@ -14362,10 +14375,10 @@
         <v>54</v>
       </c>
       <c r="D318">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E318">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F318">
         <v>757.33088991120428</v>
@@ -14391,10 +14404,10 @@
         <v>53</v>
       </c>
       <c r="D319">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E319">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F319">
         <v>999999</v>
@@ -14420,10 +14433,10 @@
         <v>71</v>
       </c>
       <c r="D320">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E320">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F320">
         <v>406.25892418089921</v>
@@ -14449,10 +14462,10 @@
         <v>59</v>
       </c>
       <c r="D321">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E321">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F321">
         <v>1392.887740048797</v>
@@ -14478,10 +14491,10 @@
         <v>51</v>
       </c>
       <c r="D322">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E322">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F322">
         <v>641.1273647229815</v>
@@ -14507,10 +14520,10 @@
         <v>67</v>
       </c>
       <c r="D323">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E323">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F323">
         <v>759.92182692766414</v>
@@ -14536,10 +14549,10 @@
         <v>46</v>
       </c>
       <c r="D324">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E324">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F324">
         <v>999999</v>
@@ -14565,10 +14578,10 @@
         <v>58</v>
       </c>
       <c r="D325">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E325">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F325">
         <v>675.58682704189698</v>
@@ -14594,10 +14607,10 @@
         <v>53</v>
       </c>
       <c r="D326">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E326">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F326">
         <v>1264.9559084666121</v>
@@ -14623,10 +14636,10 @@
         <v>61</v>
       </c>
       <c r="D327">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E327">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F327">
         <v>1717.7062159497341</v>
@@ -14652,10 +14665,10 @@
         <v>48</v>
       </c>
       <c r="D328">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E328">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F328">
         <v>953.02688240405632</v>
@@ -14681,10 +14694,10 @@
         <v>45</v>
       </c>
       <c r="D329">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E329">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F329">
         <v>160.50854816968561</v>
@@ -14710,10 +14723,10 @@
         <v>67</v>
       </c>
       <c r="D330">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E330">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F330">
         <v>852.2887315644565</v>
@@ -14739,10 +14752,10 @@
         <v>48</v>
       </c>
       <c r="D331">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E331">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F331">
         <v>652.26839389375868</v>
@@ -14768,10 +14781,10 @@
         <v>63</v>
       </c>
       <c r="D332">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E332">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F332">
         <v>952.03980669815951</v>
@@ -14797,10 +14810,10 @@
         <v>47</v>
       </c>
       <c r="D333">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E333">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F333">
         <v>415.58629744015451</v>
@@ -14826,10 +14839,10 @@
         <v>49</v>
       </c>
       <c r="D334">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E334">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F334">
         <v>496.94171975699282</v>
@@ -14855,10 +14868,10 @@
         <v>58</v>
       </c>
       <c r="D335">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E335">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F335">
         <v>1230.7572199184131</v>
@@ -14884,10 +14897,10 @@
         <v>42</v>
       </c>
       <c r="D336">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E336">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F336">
         <v>524.79429268393574</v>
@@ -14913,10 +14926,10 @@
         <v>65</v>
       </c>
       <c r="D337">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E337">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F337">
         <v>131.87869413780459</v>
@@ -14942,10 +14955,10 @@
         <v>43</v>
       </c>
       <c r="D338">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E338">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F338">
         <v>219.71145899579241</v>
@@ -14971,10 +14984,10 @@
         <v>57</v>
       </c>
       <c r="D339">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E339">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F339">
         <v>182.0133254063021</v>
@@ -15000,10 +15013,10 @@
         <v>55</v>
       </c>
       <c r="D340">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E340">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F340">
         <v>591.38137400695302</v>
@@ -15029,10 +15042,10 @@
         <v>59</v>
       </c>
       <c r="D341">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E341">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F341">
         <v>1200.4481789747001</v>
@@ -15058,10 +15071,10 @@
         <v>43</v>
       </c>
       <c r="D342">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E342">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F342">
         <v>608.48155831558779</v>
@@ -15087,10 +15100,10 @@
         <v>45</v>
       </c>
       <c r="D343">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E343">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F343">
         <v>960.28089975305704</v>
@@ -15116,10 +15129,10 @@
         <v>44</v>
       </c>
       <c r="D344">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E344">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F344">
         <v>93.532826294199367</v>
@@ -15145,10 +15158,10 @@
         <v>47</v>
       </c>
       <c r="D345">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E345">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F345">
         <v>1196.6881673472999</v>
@@ -15174,10 +15187,10 @@
         <v>71</v>
       </c>
       <c r="D346">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E346">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F346">
         <v>1056.843209013959</v>
@@ -15203,10 +15216,10 @@
         <v>49</v>
       </c>
       <c r="D347">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E347">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F347">
         <v>999999</v>
@@ -15232,10 +15245,10 @@
         <v>43</v>
       </c>
       <c r="D348">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E348">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F348">
         <v>986.83586074287746</v>
@@ -15261,10 +15274,10 @@
         <v>52</v>
       </c>
       <c r="D349">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E349">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F349">
         <v>634.52047533100904</v>
@@ -15290,10 +15303,10 @@
         <v>45</v>
       </c>
       <c r="D350">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E350">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F350">
         <v>1052.640815546031</v>
@@ -15319,10 +15332,10 @@
         <v>47</v>
       </c>
       <c r="D351">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E351">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F351">
         <v>1289.050492568156</v>
@@ -15348,10 +15361,10 @@
         <v>49</v>
       </c>
       <c r="D352">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E352">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F352">
         <v>1385.29968041865</v>
@@ -15377,10 +15390,10 @@
         <v>57</v>
       </c>
       <c r="D353">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E353">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F353">
         <v>999999</v>
@@ -15406,10 +15419,10 @@
         <v>50</v>
       </c>
       <c r="D354">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E354">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F354">
         <v>644.49558284437921</v>
@@ -15435,10 +15448,10 @@
         <v>44</v>
       </c>
       <c r="D355">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E355">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F355">
         <v>830.26576692454796</v>
@@ -15464,10 +15477,10 @@
         <v>43</v>
       </c>
       <c r="D356">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E356">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F356">
         <v>1079.1961319953689</v>
@@ -15493,10 +15506,10 @@
         <v>53</v>
       </c>
       <c r="D357">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E357">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F357">
         <v>558.21738019626741</v>
@@ -15522,10 +15535,10 @@
         <v>57</v>
       </c>
       <c r="D358">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E358">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F358">
         <v>1069.3512238301121</v>
@@ -15551,10 +15564,10 @@
         <v>42</v>
       </c>
       <c r="D359">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E359">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F359">
         <v>822.19733493347815</v>
@@ -15580,10 +15593,10 @@
         <v>44</v>
       </c>
       <c r="D360">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E360">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F360">
         <v>858.59605576988724</v>
@@ -15609,10 +15622,10 @@
         <v>67</v>
       </c>
       <c r="D361">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E361">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F361">
         <v>698.49657055153671</v>
@@ -15638,10 +15651,10 @@
         <v>51</v>
       </c>
       <c r="D362">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E362">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F362">
         <v>650.71383168388286</v>
@@ -15667,10 +15680,10 @@
         <v>69</v>
       </c>
       <c r="D363">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E363">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F363">
         <v>575.05847080325623</v>
@@ -15696,10 +15709,10 @@
         <v>44</v>
       </c>
       <c r="D364">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E364">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F364">
         <v>950.95430771786437</v>
@@ -15725,10 +15738,10 @@
         <v>63</v>
       </c>
       <c r="D365">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E365">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F365">
         <v>943.36016769301909</v>
@@ -15754,10 +15767,10 @@
         <v>65</v>
       </c>
       <c r="D366">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E366">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F366">
         <v>123.1990551326643</v>
@@ -15783,10 +15796,10 @@
         <v>46</v>
       </c>
       <c r="D367">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E367">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F367">
         <v>389.80647412637933</v>
@@ -15812,10 +15825,10 @@
         <v>55</v>
       </c>
       <c r="D368">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E368">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F368">
         <v>427.37506086504658</v>
@@ -15841,10 +15854,10 @@
         <v>61</v>
       </c>
       <c r="D369">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E369">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F369">
         <v>1027.899116049221</v>
@@ -15870,10 +15883,10 @@
         <v>52</v>
       </c>
       <c r="D370">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E370">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F370">
         <v>475.33878187489171</v>
@@ -15899,10 +15912,10 @@
         <v>51</v>
       </c>
       <c r="D371">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E371">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F371">
         <v>552.00815315617558</v>
@@ -15928,10 +15941,10 @@
         <v>59</v>
       </c>
       <c r="D372">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E372">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F372">
         <v>1150.1869315817321</v>
@@ -15957,10 +15970,10 @@
         <v>50</v>
       </c>
       <c r="D373">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E373">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F373">
         <v>953.93363406832589</v>
@@ -15986,10 +15999,10 @@
         <v>54</v>
       </c>
       <c r="D374">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E374">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F374">
         <v>961.70579709298238</v>
@@ -16015,10 +16028,10 @@
         <v>41</v>
       </c>
       <c r="D375">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E375">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F375">
         <v>19449.206435412791</v>
@@ -16044,10 +16057,10 @@
         <v>24</v>
       </c>
       <c r="D376">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E376">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F376">
         <v>19060.222306704542</v>
@@ -16073,10 +16086,10 @@
         <v>6</v>
       </c>
       <c r="D377">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E377">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F377">
         <v>19449.206435412791</v>
@@ -16102,10 +16115,10 @@
         <v>9</v>
       </c>
       <c r="D378">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E378">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F378">
         <v>19449.206435412791</v>
@@ -16131,10 +16144,10 @@
         <v>17</v>
       </c>
       <c r="D379">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E379">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F379">
         <v>19449.206435412791</v>
@@ -16160,10 +16173,10 @@
         <v>15</v>
       </c>
       <c r="D380">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E380">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F380">
         <v>19449.206435412791</v>
@@ -16189,10 +16202,10 @@
         <v>22</v>
       </c>
       <c r="D381">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E381">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F381">
         <v>19449.206435412791</v>
@@ -16218,10 +16231,10 @@
         <v>11</v>
       </c>
       <c r="D382">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E382">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F382">
         <v>19449.206435412791</v>
@@ -16247,10 +16260,10 @@
         <v>31</v>
       </c>
       <c r="D383">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E383">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F383">
         <v>19449.206435412791</v>
@@ -16276,10 +16289,10 @@
         <v>29</v>
       </c>
       <c r="D384">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E384">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F384">
         <v>19449.206435412791</v>
@@ -16305,10 +16318,10 @@
         <v>33</v>
       </c>
       <c r="D385">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E385">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F385">
         <v>19449.206435412791</v>
@@ -16334,10 +16347,10 @@
         <v>32</v>
       </c>
       <c r="D386">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E386">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F386">
         <v>19449.206435412791</v>
@@ -16363,10 +16376,10 @@
         <v>21</v>
       </c>
       <c r="D387">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E387">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F387">
         <v>19449.206435412791</v>
@@ -16392,10 +16405,10 @@
         <v>5</v>
       </c>
       <c r="D388">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E388">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F388">
         <v>19449.206435412791</v>
@@ -16421,10 +16434,10 @@
         <v>37</v>
       </c>
       <c r="D389">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E389">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F389">
         <v>19449.206435412791</v>
@@ -16450,10 +16463,10 @@
         <v>10</v>
       </c>
       <c r="D390">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E390">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F390">
         <v>19449.206435412791</v>
@@ -16479,10 +16492,10 @@
         <v>20</v>
       </c>
       <c r="D391">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E391">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F391">
         <v>19449.206435412791</v>
@@ -16508,10 +16521,10 @@
         <v>16</v>
       </c>
       <c r="D392">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E392">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F392">
         <v>19449.206435412791</v>
@@ -16537,10 +16550,10 @@
         <v>4</v>
       </c>
       <c r="D393">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E393">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F393">
         <v>19449.206435412791</v>
@@ -16566,10 +16579,10 @@
         <v>39</v>
       </c>
       <c r="D394">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E394">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F394">
         <v>17504.285791871509</v>
@@ -16595,10 +16608,10 @@
         <v>3</v>
       </c>
       <c r="D395">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E395">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F395">
         <v>19449.206435412791</v>
@@ -16624,10 +16637,10 @@
         <v>13</v>
       </c>
       <c r="D396">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E396">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F396">
         <v>19449.206435412791</v>
@@ -16653,10 +16666,10 @@
         <v>38</v>
       </c>
       <c r="D397">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E397">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F397">
         <v>19449.206435412791</v>
@@ -16682,10 +16695,10 @@
         <v>18</v>
       </c>
       <c r="D398">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E398">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F398">
         <v>19449.206435412791</v>
@@ -16711,10 +16724,10 @@
         <v>40</v>
       </c>
       <c r="D399">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E399">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F399">
         <v>19449.206435412791</v>
@@ -16740,10 +16753,10 @@
         <v>7</v>
       </c>
       <c r="D400">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E400">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F400">
         <v>19449.206435412791</v>
@@ -16769,10 +16782,10 @@
         <v>2</v>
       </c>
       <c r="D401">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E401">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F401">
         <v>19449.206435412791</v>
@@ -16798,10 +16811,10 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E402">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F402">
         <v>19449.206435412791</v>
@@ -16827,10 +16840,10 @@
         <v>23</v>
       </c>
       <c r="D403">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E403">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F403">
         <v>19449.206435412791</v>
@@ -16856,10 +16869,10 @@
         <v>8</v>
       </c>
       <c r="D404">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E404">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F404">
         <v>17504.285791871509</v>
@@ -16885,10 +16898,10 @@
         <v>14</v>
       </c>
       <c r="D405">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E405">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F405">
         <v>19449.206435412791</v>
@@ -16914,10 +16927,10 @@
         <v>12</v>
       </c>
       <c r="D406">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E406">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F406">
         <v>19449.206435412791</v>
@@ -16943,10 +16956,10 @@
         <v>36</v>
       </c>
       <c r="D407">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E407">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F407">
         <v>19449.206435412791</v>
@@ -16972,10 +16985,10 @@
         <v>30</v>
       </c>
       <c r="D408">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E408">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F408">
         <v>19449.206435412791</v>
@@ -17001,10 +17014,10 @@
         <v>26</v>
       </c>
       <c r="D409">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E409">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F409">
         <v>17504.285791871509</v>
@@ -17030,10 +17043,10 @@
         <v>34</v>
       </c>
       <c r="D410">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E410">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F410">
         <v>19449.206435412791</v>
@@ -17059,10 +17072,10 @@
         <v>19</v>
       </c>
       <c r="D411">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E411">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F411">
         <v>19449.206435412791</v>
@@ -17088,10 +17101,10 @@
         <v>1</v>
       </c>
       <c r="D412">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E412">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F412">
         <v>19449.206435412791</v>
@@ -17117,10 +17130,10 @@
         <v>28</v>
       </c>
       <c r="D413">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E413">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F413">
         <v>19449.206435412791</v>
@@ -17146,10 +17159,10 @@
         <v>77</v>
       </c>
       <c r="D414">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E414">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F414">
         <v>22950.06359378709</v>
@@ -17175,10 +17188,10 @@
         <v>89</v>
       </c>
       <c r="D415">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E415">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F415">
         <v>23339.04772249535</v>
@@ -17204,10 +17217,10 @@
         <v>72</v>
       </c>
       <c r="D416">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E416">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F416">
         <v>23339.04772249535</v>
@@ -17233,10 +17246,10 @@
         <v>73</v>
       </c>
       <c r="D417">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E417">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F417">
         <v>19838.19056412104</v>
@@ -17262,10 +17275,10 @@
         <v>79</v>
       </c>
       <c r="D418">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E418">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F418">
         <v>11669.523861247681</v>
@@ -17291,10 +17304,10 @@
         <v>75</v>
       </c>
       <c r="D419">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E419">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F419">
         <v>9335.619088998139</v>
@@ -17320,10 +17333,10 @@
         <v>64</v>
       </c>
       <c r="D420">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E420">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F420">
         <v>15948.349277038489</v>
@@ -17349,10 +17362,10 @@
         <v>25</v>
       </c>
       <c r="D421">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E421">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F421">
         <v>17504.285791871509</v>
@@ -17378,10 +17391,10 @@
         <v>82</v>
       </c>
       <c r="D422">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E422">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F422">
         <v>29173.80965311918</v>
@@ -17407,10 +17420,10 @@
         <v>62</v>
       </c>
       <c r="D423">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E423">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F423">
         <v>32674.66681149348</v>
@@ -17436,10 +17449,10 @@
         <v>60</v>
       </c>
       <c r="D424">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E424">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F424">
         <v>32674.66681149348</v>
@@ -17465,10 +17478,10 @@
         <v>66</v>
       </c>
       <c r="D425">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E425">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F425">
         <v>32674.66681149348</v>
@@ -17494,10 +17507,10 @@
         <v>70</v>
       </c>
       <c r="D426">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E426">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F426">
         <v>32674.66681149348</v>
@@ -17523,10 +17536,10 @@
         <v>88</v>
       </c>
       <c r="D427">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E427">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F427">
         <v>19449.206435412791</v>
@@ -17552,10 +17565,10 @@
         <v>68</v>
       </c>
       <c r="D428">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E428">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F428">
         <v>17504.285791871509</v>
@@ -17581,10 +17594,10 @@
         <v>85</v>
       </c>
       <c r="D429">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="E429">
-        <v>9999999</v>
+        <v>999999999</v>
       </c>
       <c r="F429">
         <v>23339.04772249535</v>
